--- a/Dataset/Alphabets-Dataset/first-draft.xlsx
+++ b/Dataset/Alphabets-Dataset/first-draft.xlsx
@@ -341,9 +341,6 @@
     <t>ڎ</t>
   </si>
   <si>
-    <t>dz</t>
-  </si>
-  <si>
     <t>U+ ‎068E</t>
   </si>
   <si>
@@ -857,9 +854,6 @@
     <t>dasen</t>
   </si>
   <si>
-    <t>dzpi</t>
-  </si>
-  <si>
     <t>herr</t>
   </si>
   <si>
@@ -977,9 +971,6 @@
     <t>ș</t>
   </si>
   <si>
-    <t>șae</t>
-  </si>
-  <si>
     <t>U+0219</t>
   </si>
   <si>
@@ -1146,6 +1137,15 @@
   </si>
   <si>
     <t>drum</t>
+  </si>
+  <si>
+    <t>č</t>
+  </si>
+  <si>
+    <t>čapi</t>
+  </si>
+  <si>
+    <t>śae</t>
   </si>
 </sst>
 </file>
@@ -1642,10 +1642,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28.2">
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.2">
@@ -1703,7 +1703,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28.2">
@@ -1732,7 +1732,7 @@
         <v>28</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.2">
@@ -1761,7 +1761,7 @@
         <v>35</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28.2">
@@ -1784,13 +1784,13 @@
         <v>41</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.2">
@@ -1813,13 +1813,13 @@
         <v>47</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.2">
@@ -1842,13 +1842,13 @@
         <v>53</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.2">
@@ -1892,13 +1892,13 @@
         <v>64</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.2">
@@ -1921,13 +1921,13 @@
         <v>70</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.2">
@@ -1971,13 +1971,13 @@
         <v>81</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.2">
@@ -2000,13 +2000,13 @@
         <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="28.2">
@@ -2026,16 +2026,16 @@
         <v>92</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.2">
@@ -2058,13 +2058,13 @@
         <v>98</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="28.2">
@@ -2093,74 +2093,74 @@
         <v>104</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28.2">
       <c r="A19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="C19" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.2">
       <c r="A20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -2169,193 +2169,193 @@
     </row>
     <row r="21" spans="1:9" ht="28.2">
       <c r="A21" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="C21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.2">
       <c r="A22" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>100</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>103</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.2">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="G23" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="28.2">
       <c r="A24" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>58</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28.2">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D25" s="4">
         <v>219</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="G25" s="4" t="s">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28.2">
       <c r="A26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28.2">
       <c r="A27" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="C27" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="D27" s="4">
         <v>635</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -2364,19 +2364,19 @@
     </row>
     <row r="28" spans="1:9" ht="28.2">
       <c r="A28" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D28" s="4">
         <v>636</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2385,19 +2385,19 @@
     </row>
     <row r="29" spans="1:9" ht="28.2">
       <c r="A29" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D29" s="4">
         <v>637</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
@@ -2406,13 +2406,13 @@
     </row>
     <row r="30" spans="1:9" ht="28.2">
       <c r="A30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D30" s="4">
         <v>638</v>
@@ -2425,19 +2425,19 @@
     </row>
     <row r="31" spans="1:9" ht="28.2">
       <c r="A31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D31" s="4">
         <v>639</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -2446,48 +2446,48 @@
     </row>
     <row r="32" spans="1:9" ht="28.2">
       <c r="A32" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="G32" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="28.2">
       <c r="A33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="C33" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D33" s="4">
         <v>641</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -2496,164 +2496,164 @@
     </row>
     <row r="34" spans="1:9" ht="28.2">
       <c r="A34" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D34" s="4">
         <v>642</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="G34" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="28.2">
       <c r="A35" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="C35" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>184</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="28.2">
       <c r="A36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="F36" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="28.2">
       <c r="A37" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D37" s="4">
         <v>644</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="28.2">
       <c r="A38" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="C38" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="E38" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F38" s="10" t="s">
-        <v>198</v>
-      </c>
       <c r="G38" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28.2">
       <c r="A39" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="C39" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>200</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>201</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
@@ -2662,135 +2662,135 @@
     </row>
     <row r="40" spans="1:9" ht="28.2">
       <c r="A40" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="C40" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="F40" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28.2">
       <c r="A41" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="C41" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="G41" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="28.2">
       <c r="A42" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B42" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="C42" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E42" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="E42" s="10" t="s">
+      <c r="F42" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>216</v>
-      </c>
       <c r="G42" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="28.2">
       <c r="A43" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="G43" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="28.2">
       <c r="A44" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B44" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="C44" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
@@ -2799,19 +2799,19 @@
     </row>
     <row r="45" spans="1:9" ht="28.2">
       <c r="A45" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="C45" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
@@ -2820,99 +2820,99 @@
     </row>
     <row r="46" spans="1:9" ht="28.2">
       <c r="A46" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="C46" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="28.2">
       <c r="A47" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="C47" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="G47" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="28.2">
       <c r="A48" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B48" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="C48" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="E48" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>244</v>
-      </c>
       <c r="F48" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="28.2">
       <c r="A49" s="1"/>
       <c r="B49" s="9"/>
       <c r="C49" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
@@ -2922,19 +2922,19 @@
     </row>
     <row r="50" spans="1:9" ht="28.2">
       <c r="A50" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B50" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="C50" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>249</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
@@ -2945,10 +2945,10 @@
       <c r="A51" s="1"/>
       <c r="B51" s="9"/>
       <c r="C51" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
@@ -2958,19 +2958,19 @@
     </row>
     <row r="52" spans="1:9" ht="28.2">
       <c r="A52" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B52" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>254</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -2979,19 +2979,19 @@
     </row>
     <row r="53" spans="1:9" ht="28.2">
       <c r="A53" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="C53" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E53" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
@@ -3002,10 +3002,10 @@
       <c r="A54" s="1"/>
       <c r="B54" s="9"/>
       <c r="C54" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
@@ -3015,19 +3015,19 @@
     </row>
     <row r="55" spans="1:9" ht="28.2">
       <c r="A55" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="C55" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>260</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
@@ -3036,19 +3036,19 @@
     </row>
     <row r="56" spans="1:9" ht="28.2">
       <c r="A56" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>264</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -3057,19 +3057,19 @@
     </row>
     <row r="57" spans="1:9" ht="28.2">
       <c r="A57" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="C57" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="E57" s="10" t="s">
         <v>268</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>269</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>

--- a/Dataset/Alphabets-Dataset/first-draft.xlsx
+++ b/Dataset/Alphabets-Dataset/first-draft.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="375">
   <si>
     <t>Nastaliq</t>
   </si>
@@ -1146,6 +1146,9 @@
   </si>
   <si>
     <t>śae</t>
+  </si>
+  <si>
+    <t>Gloss (EN)</t>
   </si>
 </sst>
 </file>
@@ -1642,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>334</v>
